--- a/Assets/DataCSV/MixMaster.xlsx
+++ b/Assets/DataCSV/MixMaster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KEIYA\Documents\GitHub\MixMaster\Assets\DataCSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7274DB0C-1BA5-4620-8C5D-7E80131D120B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{676661AC-F779-49C0-8B69-603521DAEF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F5B45C5E-FDA1-433E-B65D-DA276FD740E0}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F5B45C5E-FDA1-433E-B65D-DA276FD740E0}"/>
   </bookViews>
   <sheets>
     <sheet name="モンスター" sheetId="3" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="156">
   <si>
     <t>各マップに祭壇が設置されていて各モンスター用の強化項目がある。</t>
     <rPh sb="0" eb="1">
@@ -1388,6 +1388,34 @@
   </si>
   <si>
     <t>雷耐性</t>
+  </si>
+  <si>
+    <t>素材名</t>
+    <rPh sb="0" eb="2">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒼澄の粘晶</t>
+  </si>
+  <si>
+    <t>灼熱の粘晶</t>
+  </si>
+  <si>
+    <t>翠命の粘晶</t>
+  </si>
+  <si>
+    <t>炎牙獣の猛牙</t>
+  </si>
+  <si>
+    <t>氷牙獣の凍牙</t>
+  </si>
+  <si>
+    <t>虹幻の粘晶</t>
   </si>
 </sst>
 </file>
@@ -1427,7 +1455,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -1846,13 +1874,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1962,6 +2034,18 @@
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -2298,14 +2382,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{026CAAB4-E721-4B0C-B2B7-A4F02A2A1DAB}">
-  <dimension ref="A1:AG7"/>
+  <dimension ref="A1:AH7"/>
   <sheetFormatPr defaultColWidth="7" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="7" style="4"/>
     <col min="2" max="16384" width="7" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:34" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>62</v>
       </c>
@@ -2378,35 +2462,38 @@
       <c r="X1" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Y1" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="Z1" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="Z1" s="33" t="s">
+      <c r="AA1" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="AA1" s="33" t="s">
+      <c r="AB1" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="AB1" s="25" t="s">
+      <c r="AC1" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="AC1" s="7" t="s">
+      <c r="AD1" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="AD1" s="7" t="s">
+      <c r="AE1" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="AE1" s="8" t="s">
+      <c r="AF1" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="AF1" s="33" t="s">
+      <c r="AG1" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="AG1" s="29" t="s">
+      <c r="AH1" s="29" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A2" s="9" t="s">
         <v>64</v>
       </c>
@@ -2479,35 +2566,38 @@
       <c r="X2" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="Y2" s="11">
+      <c r="Y2" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="Z2" s="11">
         <v>0.2</v>
       </c>
-      <c r="Z2" s="34">
+      <c r="AA2" s="34">
         <v>5</v>
       </c>
-      <c r="AA2" s="34">
+      <c r="AB2" s="34">
         <v>10</v>
       </c>
-      <c r="AB2" s="26" t="s">
+      <c r="AC2" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="AC2" s="10">
+      <c r="AD2" s="10">
         <v>7</v>
       </c>
-      <c r="AD2" s="10">
+      <c r="AE2" s="10">
         <v>3</v>
       </c>
-      <c r="AE2" s="11" t="b">
+      <c r="AF2" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="AF2" s="34" t="s">
+      <c r="AG2" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="AG2" s="30" t="s">
+      <c r="AH2" s="30" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>65</v>
       </c>
@@ -2580,35 +2670,38 @@
       <c r="X3" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="Y3" s="13">
+      <c r="Y3" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="Z3" s="13">
         <v>0.2</v>
       </c>
-      <c r="Z3" s="35">
+      <c r="AA3" s="35">
         <v>7</v>
       </c>
-      <c r="AA3" s="35">
+      <c r="AB3" s="35">
         <v>12</v>
       </c>
-      <c r="AB3" s="27" t="s">
+      <c r="AC3" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="AC3" s="5">
+      <c r="AD3" s="5">
         <v>7.5</v>
       </c>
-      <c r="AD3" s="5">
+      <c r="AE3" s="5">
         <v>3</v>
       </c>
-      <c r="AE3" s="13" t="b">
+      <c r="AF3" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="AF3" s="35" t="s">
+      <c r="AG3" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="AG3" s="31" t="s">
+      <c r="AH3" s="31" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A4" s="12" t="s">
         <v>66</v>
       </c>
@@ -2681,35 +2774,38 @@
       <c r="X4" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="Y4" s="13">
+      <c r="Y4" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z4" s="13">
         <v>0.22</v>
       </c>
-      <c r="Z4" s="35">
+      <c r="AA4" s="35">
         <v>10</v>
       </c>
-      <c r="AA4" s="35">
+      <c r="AB4" s="35">
         <v>15</v>
       </c>
-      <c r="AB4" s="27" t="s">
+      <c r="AC4" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="AC4" s="5">
+      <c r="AD4" s="5">
         <v>8.5</v>
       </c>
-      <c r="AD4" s="5">
+      <c r="AE4" s="5">
         <v>3</v>
       </c>
-      <c r="AE4" s="13" t="b">
+      <c r="AF4" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="AF4" s="35" t="s">
+      <c r="AG4" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="AG4" s="31" t="s">
+      <c r="AH4" s="31" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A5" s="12" t="s">
         <v>67</v>
       </c>
@@ -2782,35 +2878,38 @@
       <c r="X5" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="Y5" s="13">
+      <c r="Y5" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z5" s="13">
         <v>0.25</v>
       </c>
-      <c r="Z5" s="35">
+      <c r="AA5" s="35">
         <v>15</v>
       </c>
-      <c r="AA5" s="35">
+      <c r="AB5" s="35">
         <v>20</v>
       </c>
-      <c r="AB5" s="27" t="s">
+      <c r="AC5" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="AC5" s="5">
-        <v>0</v>
-      </c>
       <c r="AD5" s="5">
         <v>0</v>
       </c>
-      <c r="AE5" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="35" t="s">
+      <c r="AE5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="AG5" s="31" t="s">
+      <c r="AH5" s="31" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>68</v>
       </c>
@@ -2883,35 +2982,38 @@
       <c r="X6" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="Y6" s="13">
+      <c r="Y6" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z6" s="13">
         <v>0.25</v>
       </c>
-      <c r="Z6" s="35">
+      <c r="AA6" s="35">
         <v>20</v>
       </c>
-      <c r="AA6" s="35">
+      <c r="AB6" s="35">
         <v>25</v>
       </c>
-      <c r="AB6" s="27" t="s">
+      <c r="AC6" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="AC6" s="5">
-        <v>0</v>
-      </c>
       <c r="AD6" s="5">
         <v>0</v>
       </c>
-      <c r="AE6" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="35" t="s">
+      <c r="AE6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="AG6" s="31" t="s">
+      <c r="AH6" s="31" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:34" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="14" t="s">
         <v>69</v>
       </c>
@@ -2984,31 +3086,34 @@
       <c r="X7" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="Y7" s="16">
+      <c r="Y7" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="Z7" s="16">
         <v>0.3</v>
-      </c>
-      <c r="Z7" s="36">
-        <v>40</v>
       </c>
       <c r="AA7" s="36">
         <v>40</v>
       </c>
-      <c r="AB7" s="28" t="s">
+      <c r="AB7" s="36">
+        <v>40</v>
+      </c>
+      <c r="AC7" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="AC7" s="15">
+      <c r="AD7" s="15">
         <v>10</v>
       </c>
-      <c r="AD7" s="15">
+      <c r="AE7" s="15">
         <v>4</v>
       </c>
-      <c r="AE7" s="16" t="b">
+      <c r="AF7" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="AF7" s="36" t="s">
+      <c r="AG7" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="AG7" s="32" t="s">
+      <c r="AH7" s="32" t="s">
         <v>136</v>
       </c>
     </row>
@@ -3034,13 +3139,13 @@
           <x14:formula1>
             <xm:f>入力規制リスト!$B$1:$B$7</xm:f>
           </x14:formula1>
-          <xm:sqref>AB2:AB1001</xm:sqref>
+          <xm:sqref>AC2:AC1001</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0B99545A-6AA4-491E-9D9E-8F013142E718}">
           <x14:formula1>
             <xm:f>入力規制リスト!$D$1:$D$2</xm:f>
           </x14:formula1>
-          <xm:sqref>AE2:AE1001</xm:sqref>
+          <xm:sqref>AF2:AF1001</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Assets/DataCSV/MixMaster.xlsx
+++ b/Assets/DataCSV/MixMaster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KEIYA\Documents\GitHub\MixMaster\Assets\DataCSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{676661AC-F779-49C0-8B69-603521DAEF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981BB776-423C-43CF-850E-7A1F53AD4A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F5B45C5E-FDA1-433E-B65D-DA276FD740E0}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{F5B45C5E-FDA1-433E-B65D-DA276FD740E0}"/>
   </bookViews>
   <sheets>
     <sheet name="モンスター" sheetId="3" r:id="rId1"/>
@@ -2054,6 +2054,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFC08E1E"/>
+      <color rgb="FF9C7218"/>
+      <color rgb="FF0E3384"/>
+      <color rgb="FF007DEE"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2063,6 +2071,92 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="四角形: 角を丸くする 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A56EC8A-3290-CB39-1353-883D92281638}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1905000" cy="952500"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 14667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="50000">
+              <a:srgbClr val="007DEE"/>
+            </a:gs>
+            <a:gs pos="0">
+              <a:srgbClr val="0E3384"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:srgbClr val="0E3384"/>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="10800000" scaled="0"/>
+        </a:gradFill>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:srgbClr val="C08E1E"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3707,11 +3801,13 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="16384" width="12.5" style="1"/>
+    <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="12.5" style="1"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Assets/DataCSV/MixMaster.xlsx
+++ b/Assets/DataCSV/MixMaster.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KEIYA\Documents\GitHub\MixMaster\Assets\DataCSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981BB776-423C-43CF-850E-7A1F53AD4A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39E87D5-D5F5-4E6A-ABDE-22A95F8AE2AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{F5B45C5E-FDA1-433E-B65D-DA276FD740E0}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{F5B45C5E-FDA1-433E-B65D-DA276FD740E0}"/>
   </bookViews>
   <sheets>
     <sheet name="モンスター" sheetId="3" r:id="rId1"/>
     <sheet name="称号" sheetId="5" r:id="rId2"/>
-    <sheet name="入力規制リスト" sheetId="4" r:id="rId3"/>
-    <sheet name="画像編集用" sheetId="1" r:id="rId4"/>
-    <sheet name="仕様メモ" sheetId="2" r:id="rId5"/>
+    <sheet name="マップ" sheetId="6" r:id="rId3"/>
+    <sheet name="入力規制リスト" sheetId="4" r:id="rId4"/>
+    <sheet name="画像編集用" sheetId="1" r:id="rId5"/>
+    <sheet name="仕様メモ" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="175">
   <si>
     <t>各マップに祭壇が設置されていて各モンスター用の強化項目がある。</t>
     <rPh sb="0" eb="1">
@@ -1294,9 +1295,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>MAT_001</t>
-  </si>
-  <si>
     <t>TITLE_001</t>
   </si>
   <si>
@@ -1416,13 +1414,84 @@
   </si>
   <si>
     <t>虹幻の粘晶</t>
+  </si>
+  <si>
+    <t>MapID</t>
+  </si>
+  <si>
+    <t>MAP_001</t>
+  </si>
+  <si>
+    <t>始まりの平野</t>
+  </si>
+  <si>
+    <t>スライムとボアが生息する平原</t>
+  </si>
+  <si>
+    <t>平野_テスト</t>
+  </si>
+  <si>
+    <t>マップの説明</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サムネイル画像</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地形生成用JSON名</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノーマルモンスター1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノーマルモンスター2</t>
+  </si>
+  <si>
+    <t>ノーマルモンスター3</t>
+  </si>
+  <si>
+    <t>ノーマルモンスター4</t>
+  </si>
+  <si>
+    <t>ノーマルモンスター5</t>
+  </si>
+  <si>
+    <t>ボスモンスター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダンジョン固有素材ID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>推奨レベル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通常モンスターの出現レベル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>強敵の出現レベル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MAT_001</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MATD_001</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1443,6 +1512,17 @@
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -1919,12 +1999,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2048,8 +2129,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="1" xr:uid="{815D33BA-1CA3-4931-8A1C-5CD2B7DA8A26}"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2477,13 +2574,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{026CAAB4-E721-4B0C-B2B7-A4F02A2A1DAB}">
   <dimension ref="A1:AH7"/>
-  <sheetFormatPr defaultColWidth="7" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="7" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="7" style="4"/>
     <col min="2" max="16384" width="7" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:34" ht="19.5" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>62</v>
       </c>
@@ -2539,7 +2636,7 @@
         <v>85</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T1" s="7" t="s">
         <v>86</v>
@@ -2557,7 +2654,7 @@
         <v>90</v>
       </c>
       <c r="Y1" s="37" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Z1" s="8" t="s">
         <v>91</v>
@@ -2587,7 +2684,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:34">
       <c r="A2" s="9" t="s">
         <v>64</v>
       </c>
@@ -2658,10 +2755,10 @@
         <v>8</v>
       </c>
       <c r="X2" s="26" t="s">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="Y2" s="38" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Z2" s="11">
         <v>0.2</v>
@@ -2685,13 +2782,13 @@
         <v>1</v>
       </c>
       <c r="AG2" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="AH2" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="AH2" s="30" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:34">
       <c r="A3" s="12" t="s">
         <v>65</v>
       </c>
@@ -2762,10 +2859,10 @@
         <v>8</v>
       </c>
       <c r="X3" s="27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Y3" s="39" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Z3" s="13">
         <v>0.2</v>
@@ -2789,13 +2886,13 @@
         <v>1</v>
       </c>
       <c r="AG3" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH3" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="AH3" s="31" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:34">
       <c r="A4" s="12" t="s">
         <v>66</v>
       </c>
@@ -2866,10 +2963,10 @@
         <v>9</v>
       </c>
       <c r="X4" s="27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Y4" s="39" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Z4" s="13">
         <v>0.22</v>
@@ -2893,13 +2990,13 @@
         <v>1</v>
       </c>
       <c r="AG4" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH4" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="AH4" s="31" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:34">
       <c r="A5" s="12" t="s">
         <v>67</v>
       </c>
@@ -2970,10 +3067,10 @@
         <v>10</v>
       </c>
       <c r="X5" s="27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y5" s="39" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Z5" s="13">
         <v>0.25</v>
@@ -2985,7 +3082,7 @@
         <v>20</v>
       </c>
       <c r="AC5" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AD5" s="5">
         <v>0</v>
@@ -2997,13 +3094,13 @@
         <v>0</v>
       </c>
       <c r="AG5" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH5" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="AH5" s="31" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:34">
       <c r="A6" s="12" t="s">
         <v>68</v>
       </c>
@@ -3074,10 +3171,10 @@
         <v>11</v>
       </c>
       <c r="X6" s="27" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y6" s="39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Z6" s="13">
         <v>0.25</v>
@@ -3089,7 +3186,7 @@
         <v>25</v>
       </c>
       <c r="AC6" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AD6" s="5">
         <v>0</v>
@@ -3101,13 +3198,13 @@
         <v>0</v>
       </c>
       <c r="AG6" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="AH6" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="AH6" s="31" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="7" spans="1:34" ht="19.5" thickBot="1">
       <c r="A7" s="14" t="s">
         <v>69</v>
       </c>
@@ -3178,10 +3275,10 @@
         <v>15</v>
       </c>
       <c r="X7" s="28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y7" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Z7" s="16">
         <v>0.3</v>
@@ -3205,10 +3302,10 @@
         <v>1</v>
       </c>
       <c r="AG7" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="AH7" s="32" t="s">
         <v>135</v>
-      </c>
-      <c r="AH7" s="32" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -3250,13 +3347,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{010777AF-B02F-4786-8B75-A28E61D11A7F}">
   <dimension ref="A1:U7"/>
-  <sheetFormatPr defaultColWidth="7" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="7" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="7" style="4"/>
     <col min="2" max="16384" width="7" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:21" ht="19.5" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>62</v>
       </c>
@@ -3306,7 +3403,7 @@
         <v>85</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R1" s="7" t="s">
         <v>86</v>
@@ -3318,15 +3415,15 @@
         <v>91</v>
       </c>
       <c r="U1" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="22" t="s">
         <v>141</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>142</v>
       </c>
       <c r="C2" s="26">
         <v>0.1</v>
@@ -3386,12 +3483,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:21">
       <c r="A3" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C3" s="27">
         <v>0.05</v>
@@ -3451,12 +3548,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:21">
       <c r="A4" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C4" s="27">
         <v>0.2</v>
@@ -3516,12 +3613,12 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:21">
       <c r="A5" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" s="27">
         <v>0.25</v>
@@ -3581,12 +3678,12 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:21">
       <c r="A6" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C6" s="27">
         <v>0.3</v>
@@ -3646,12 +3743,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:21" ht="19.5" thickBot="1">
       <c r="A7" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C7" s="28">
         <v>0.35</v>
@@ -3718,76 +3815,105 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6360F0-8862-4F85-9C19-3480B0A33C25}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEFD005F-94FF-4137-9A6E-70C9AED842AA}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultColWidth="15.375" defaultRowHeight="18.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="16384" width="15.375" style="42"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D1" t="b">
+    <row r="1" spans="1:15" s="41" customFormat="1" ht="18.75" customHeight="1">
+      <c r="A1" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>160</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="I1" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="J1" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K1" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="L1" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="M1" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="N1" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="O1" s="43" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" s="41" customFormat="1" ht="18.75" customHeight="1">
+      <c r="A2" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>158</v>
+      </c>
+      <c r="D2" s="44">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B7" t="s">
-        <v>138</v>
+      <c r="E2" s="44" t="s">
+        <v>159</v>
+      </c>
+      <c r="F2" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="K2" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="L2" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="M2" s="45">
+        <v>1</v>
+      </c>
+      <c r="N2" s="45">
+        <v>1</v>
+      </c>
+      <c r="O2" s="45">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3797,9 +3923,88 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6360F0-8862-4F85-9C19-3480B0A33C25}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2789E06E-BA01-416D-B10A-FD884F219AEC}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
     <col min="2" max="16384" width="12.5" style="1"/>
@@ -3811,290 +4016,290 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F20D1F1-1762-4F84-A326-8DC0937774F6}">
   <dimension ref="A1:A62"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="217.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:1">
       <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:1">
       <c r="A11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:1">
       <c r="A12" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:1">
       <c r="A14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:1">
       <c r="A15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:1">
       <c r="A16" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:1">
       <c r="A25" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:1">
       <c r="A26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:1">
       <c r="A27" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:1">
       <c r="A28" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:1">
       <c r="A29" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:1">
       <c r="A31" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:1">
       <c r="A32" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:1">
       <c r="A33" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:1">
       <c r="A34" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:1">
       <c r="A35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:1">
       <c r="A36" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:1">
       <c r="A37" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:1">
       <c r="A38" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:1">
       <c r="A39" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:1">
       <c r="A41" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:1" ht="93.75" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:1" ht="93.75">
       <c r="A42" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:1">
       <c r="A43" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:1">
       <c r="A44" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:1">
       <c r="A45" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:1">
       <c r="A46" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:1">
       <c r="A47" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:1">
       <c r="A49" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:1">
       <c r="A50" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:1">
       <c r="A51" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:1">
       <c r="A52" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:1">
       <c r="A53" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:1">
       <c r="A54" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:1">
       <c r="A55" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:1">
       <c r="A56" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:1">
       <c r="A58" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:1">
       <c r="A59" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:1">
       <c r="A60" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:1">
       <c r="A61" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:1">
       <c r="A62" t="s">
         <v>54</v>
       </c>
